--- a/data/AttributeRule.xlsx
+++ b/data/AttributeRule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,10 +447,12 @@
           <t>scheme_name_max_len</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>alloc_efficiency_bonus</t>
+        </is>
+      </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -480,6 +482,11 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>方案名最大字符数</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>加点效率系数 b(E(n)=n×(1+b×n÷s);0=纯线性;s 与除数由池表现算)</t>
         </is>
       </c>
     </row>
@@ -501,6 +508,9 @@
       </c>
       <c r="F6" t="n">
         <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/AttributeRule.xlsx
+++ b/data/AttributeRule.xlsx
@@ -509,8 +509,8 @@
       <c r="F6" t="n">
         <v>12</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.2</v>
+      <c r="G6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
